--- a/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/Employment and full-time education rates among 18–24 year olds, Apr 2025-Mar 2026.xlsx
+++ b/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/Employment and full-time education rates among 18–24 year olds, Apr 2025-Mar 2026.xlsx
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
